--- a/Scripts_run/Manual_Monitoring/Reports/Manual_Monitoring_Report.xlsx
+++ b/Scripts_run/Manual_Monitoring/Reports/Manual_Monitoring_Report.xlsx
@@ -2004,16 +2004,16 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>32</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19357</v>
+        <v>26043</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
